--- a/outputs/per-fund/vc-investments-figment-capital.xlsx
+++ b/outputs/per-fund/vc-investments-figment-capital.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Figment Capital. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Figment Capital. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -9681,11 +9681,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital</t>
+          <t>coinbase-ventures, coinfund, figment-capital</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -9866,11 +9866,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, figment-capital</t>
+          <t>alliance-dao, coinbase-ventures, delphi-ventures, figment-capital, iosg-ventures</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -10047,11 +10047,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, polychain</t>
+          <t>figment-capital, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -10110,11 +10110,11 @@
         <v>1</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, multicoin-capital</t>
+          <t>alameda-research, alliance-dao, animoca-brands, figment-capital, hashkey-capital, huobi-ventures, mechanism-capital, multicoin-capital, polygon-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -10169,11 +10169,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital</t>
+          <t>alameda-research, arrington-capital, coinfund, dragonfly, fenbushi-capital, figment-capital, hashed, hashkey-capital, huobi-ventures</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -10232,11 +10232,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, multicoin-capital</t>
+          <t>animoca-brands, coinbase-ventures, coinfund, digital-currency-group, figment-capital, hashed, jump-crypto, multicoin-capital</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -10358,11 +10358,11 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>figment-capital, hypersphere</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -10423,11 +10423,11 @@
         <v>2</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, lemniscap</t>
+          <t>blockchain-capital, coinfund, figment-capital, hashed, hypersphere, lemniscap</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -10486,11 +10486,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital</t>
+          <t>blockchain-capital, coinbase-ventures, figment-capital, gsr, longhash-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -10549,11 +10549,11 @@
         <v>1</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, gnosis-vc, polychain, robot-ventures</t>
+          <t>1kx, amber-group, circle-ventures, figment-capital, gnosis-vc, hack-vc, hypersphere, polychain, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -10612,11 +10612,11 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital</t>
+          <t>animoca-brands, coinbase-ventures, figment-capital</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -10742,11 +10742,11 @@
         <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>big-brain-holdings, figment-capital</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -10805,11 +10805,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, gsr, hypersphere, longhash-ventures, maven11</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -10931,11 +10931,11 @@
         <v>2</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, polychain</t>
+          <t>blockchain-capital, figment-capital, polychain</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -11057,11 +11057,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>figment-capital, gsr, spartan-group</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -11120,11 +11120,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>circle-ventures, coinfund, figment-capital, galaxy-digital</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -11185,11 +11185,11 @@
         <v>2</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, delphi-ventures, figment-capital, maven11, polychain</t>
+          <t>bain-capital-crypto, blockchain-capital, coinbase-ventures, delphi-ventures, figment-capital, galaxy-digital, jump-crypto, maven11, mh-ventures, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -11311,11 +11311,11 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, lemniscap, polychain</t>
+          <t>figment-capital, huobi-ventures, lemniscap, polychain</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -11437,11 +11437,11 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>figment-capital, spartan-group</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -11500,11 +11500,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
+          <t>1kx, delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -11563,11 +11563,11 @@
         <v>2</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, robot-ventures</t>
+          <t>fenbushi-capital, figment-capital, iosg-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -11626,11 +11626,11 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, delphi-ventures, figment-capital, maven11</t>
+          <t>bain-capital-crypto, blockchain-capital, delphi-ventures, fenbushi-capital, figment-capital, galaxy-digital, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -11691,11 +11691,11 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, iosg-ventures, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -11754,11 +11754,11 @@
         <v>3</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, maven11</t>
+          <t>blockchain-capital, coinbase-ventures, digital-currency-group, figment-capital, maven11</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -11817,11 +11817,11 @@
         <v>2</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, founders-fund</t>
+          <t>dragonfly, figment-capital, founders-fund, sevenx-ventures</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -11880,11 +11880,11 @@
         <v>2</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital</t>
+          <t>big-brain-holdings, delphi-ventures, figment-capital, hack-vc</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -11943,11 +11943,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, multicoin-capital</t>
+          <t>animoca-brands, arrington-capital, figment-capital, mechanism-capital, mh-ventures, multicoin-capital, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -12006,11 +12006,11 @@
         <v>2</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital</t>
+          <t>coinbase-ventures, figment-capital, galaxy-digital, mirana-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -12069,11 +12069,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11, polychain, robot-ventures</t>
+          <t>figment-capital, hack-vc, maven11, mh-ventures, okx-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -12132,11 +12132,11 @@
         <v>1</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>figment-capital, foresight-ventures, hack-vc, hashkey-capital, huobi-ventures, hypersphere, iosg-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -12195,11 +12195,11 @@
         <v>3</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, dragonfly, figment-capital, founders-fund</t>
+          <t>alliance-dao, cyber-fund, dragonfly, figment-capital, foresight-ventures, founders-fund, hashkey-capital, longhash-ventures, mirana-ventures, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -12254,11 +12254,11 @@
         <v>2</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, galaxy-digital, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -12317,11 +12317,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, robot-ventures</t>
+          <t>big-brain-holdings, dragonfly, figment-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -12380,11 +12380,11 @@
         <v>2</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>1kx, figment-capital, maven11</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -12508,11 +12508,11 @@
         <v>1</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures</t>
+          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -12630,11 +12630,11 @@
         <v>3</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, figment-capital</t>
+          <t>1kx, cyber-fund, figment-capital, gsr, hashkey-capital</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -12693,11 +12693,11 @@
         <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, robot-ventures</t>
+          <t>fenbushi-capital, figment-capital, hack-vc, robot-ventures</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -12815,11 +12815,11 @@
         <v>2</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>big-brain-holdings, figment-capital</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -12937,11 +12937,11 @@
         <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures</t>
+          <t>alliance-dao, big-brain-holdings, delphi-ventures, figment-capital, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -13057,11 +13057,11 @@
         <v>2</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, robot-ventures</t>
+          <t>coinbase-ventures, figment-capital, hashkey-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -13120,11 +13120,11 @@
         <v>2</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>amber-group, figment-capital</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -13246,11 +13246,11 @@
         <v>0</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>figment-capital</t>
+          <t>big-brain-holdings, figment-capital</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -13435,11 +13435,11 @@
         <v>1</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, paradigm</t>
+          <t>figment-capital, gsr, paradigm</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -16615,19 +16615,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
